--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_YORK_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_YORK_2011.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C94">
@@ -5917,7 +5917,7 @@
         <v>20</v>
       </c>
       <c r="D309">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="310">
@@ -6709,7 +6709,7 @@
         <v>20</v>
       </c>
       <c r="D353">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="354">
@@ -8455,7 +8455,7 @@
         <v>20</v>
       </c>
       <c r="D450">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="451">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C466">
@@ -13783,7 +13783,7 @@
         <v>199</v>
       </c>
       <c r="D746">
-        <v>0.009173888991333</v>
+        <v>0.009173888991333002</v>
       </c>
     </row>
     <row r="747">
@@ -14053,7 +14053,7 @@
         <v>20</v>
       </c>
       <c r="D761">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="762">
@@ -14377,7 +14377,7 @@
         <v>200</v>
       </c>
       <c r="D779">
-        <v>0.009219988936013</v>
+        <v>0.009219988936013002</v>
       </c>
     </row>
     <row r="780">
@@ -14521,7 +14521,7 @@
         <v>20</v>
       </c>
       <c r="D787">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="788">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C908">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C946">
@@ -18319,7 +18319,7 @@
         <v>20</v>
       </c>
       <c r="D998">
-        <v>0.000921998893601</v>
+        <v>0.0009219988936010002</v>
       </c>
     </row>
     <row r="999">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1053">
